--- a/docs/data-templates/samples/年度预算范例.xlsx
+++ b/docs/data-templates/samples/年度预算范例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="31229" windowHeight="14212"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1472,10 +1472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P78"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="12.6283185840708" defaultRowHeight="11.85"/>
   <cols>
-    <col min="1" max="16383" width="12.625" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="12.625" customWidth="1"/>
+    <col min="1" max="16383" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="12.6283185840708" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="51" customHeight="1" spans="1:16">
@@ -1519,34 +1519,34 @@
         <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:16">
@@ -1554,34 +1554,34 @@
         <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:16">
@@ -1589,34 +1589,34 @@
         <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:16">
@@ -1624,34 +1624,34 @@
         <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:16">
@@ -1659,34 +1659,34 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:16">
@@ -1694,34 +1694,34 @@
         <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:16">
@@ -1729,34 +1729,34 @@
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:16">
@@ -1764,34 +1764,34 @@
         <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:16">
@@ -1799,34 +1799,34 @@
         <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:16">
@@ -1834,34 +1834,34 @@
         <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:16">
@@ -1869,34 +1869,34 @@
         <v>21</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:16">
@@ -1904,34 +1904,34 @@
         <v>22</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:16">
@@ -1939,34 +1939,34 @@
         <v>23</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:16">
@@ -1974,34 +1974,34 @@
         <v>24</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:16">
@@ -2009,34 +2009,34 @@
         <v>25</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:11">
@@ -2044,34 +2044,34 @@
         <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:11">
@@ -2079,34 +2079,34 @@
         <v>27</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:11">
@@ -2114,34 +2114,34 @@
         <v>28</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K19" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:11">
@@ -2149,34 +2149,34 @@
         <v>29</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K20" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:11">
@@ -2184,34 +2184,34 @@
         <v>30</v>
       </c>
       <c r="B21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K21" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:11">
@@ -2219,34 +2219,34 @@
         <v>31</v>
       </c>
       <c r="B22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:11">
@@ -2254,34 +2254,34 @@
         <v>32</v>
       </c>
       <c r="B23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K23" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:11">
@@ -2289,34 +2289,34 @@
         <v>33</v>
       </c>
       <c r="B24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K24" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:11">
@@ -2324,34 +2324,34 @@
         <v>34</v>
       </c>
       <c r="B25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:11">
@@ -2359,34 +2359,34 @@
         <v>35</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:11">
@@ -2394,34 +2394,34 @@
         <v>36</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:11">
@@ -2429,34 +2429,34 @@
         <v>37</v>
       </c>
       <c r="B28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K28" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:11">
@@ -2464,34 +2464,34 @@
         <v>38</v>
       </c>
       <c r="B29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K29" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:11">
@@ -2499,34 +2499,34 @@
         <v>39</v>
       </c>
       <c r="B30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:11">
@@ -2534,34 +2534,34 @@
         <v>40</v>
       </c>
       <c r="B31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:11">
@@ -2569,34 +2569,34 @@
         <v>41</v>
       </c>
       <c r="B32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K32" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:11">
@@ -2604,34 +2604,34 @@
         <v>42</v>
       </c>
       <c r="B33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:11">
@@ -2639,34 +2639,34 @@
         <v>43</v>
       </c>
       <c r="B34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:11">
@@ -2674,34 +2674,34 @@
         <v>44</v>
       </c>
       <c r="B35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:11">
@@ -2709,34 +2709,34 @@
         <v>45</v>
       </c>
       <c r="B36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K36" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:11">
@@ -2744,34 +2744,34 @@
         <v>46</v>
       </c>
       <c r="B37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K37" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:11">
@@ -2779,34 +2779,34 @@
         <v>47</v>
       </c>
       <c r="B38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K38" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:11">
@@ -2814,34 +2814,34 @@
         <v>48</v>
       </c>
       <c r="B39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:11">
@@ -2849,34 +2849,34 @@
         <v>49</v>
       </c>
       <c r="B40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K40" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:11">
@@ -2884,34 +2884,34 @@
         <v>50</v>
       </c>
       <c r="B41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K41" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:11">
@@ -2919,34 +2919,34 @@
         <v>51</v>
       </c>
       <c r="B42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K42" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:11">
@@ -2954,34 +2954,34 @@
         <v>52</v>
       </c>
       <c r="B43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K43" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:11">
@@ -2989,34 +2989,34 @@
         <v>53</v>
       </c>
       <c r="B44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K44" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:11">
@@ -3024,34 +3024,34 @@
         <v>54</v>
       </c>
       <c r="B45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K45" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:11">
@@ -3059,34 +3059,34 @@
         <v>55</v>
       </c>
       <c r="B46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K46" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:11">
@@ -3094,34 +3094,34 @@
         <v>56</v>
       </c>
       <c r="B47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K47" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:11">
@@ -3129,34 +3129,34 @@
         <v>57</v>
       </c>
       <c r="B48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K48" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:11">
@@ -3164,34 +3164,34 @@
         <v>58</v>
       </c>
       <c r="B49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K49" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:11">
@@ -3199,34 +3199,34 @@
         <v>59</v>
       </c>
       <c r="B50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K50" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:11">
@@ -3234,34 +3234,34 @@
         <v>60</v>
       </c>
       <c r="B51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K51" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:11">
@@ -3269,34 +3269,34 @@
         <v>61</v>
       </c>
       <c r="B52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K52" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:11">
@@ -3304,34 +3304,34 @@
         <v>62</v>
       </c>
       <c r="B53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K53" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:11">
@@ -3339,34 +3339,34 @@
         <v>63</v>
       </c>
       <c r="B54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K54" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:11">
@@ -3374,34 +3374,34 @@
         <v>64</v>
       </c>
       <c r="B55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K55" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:11">
@@ -3409,34 +3409,34 @@
         <v>65</v>
       </c>
       <c r="B56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K56" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:11">
@@ -3444,34 +3444,34 @@
         <v>66</v>
       </c>
       <c r="B57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K57" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:11">
@@ -3479,34 +3479,34 @@
         <v>67</v>
       </c>
       <c r="B58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K58" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:11">
@@ -3514,34 +3514,34 @@
         <v>68</v>
       </c>
       <c r="B59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K59" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:11">
@@ -3549,34 +3549,34 @@
         <v>69</v>
       </c>
       <c r="B60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K60" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:11">
@@ -3584,34 +3584,34 @@
         <v>70</v>
       </c>
       <c r="B61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K61" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:11">
@@ -3619,34 +3619,34 @@
         <v>71</v>
       </c>
       <c r="B62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K62" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:11">
@@ -3654,34 +3654,34 @@
         <v>72</v>
       </c>
       <c r="B63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K63" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:11">
@@ -3689,34 +3689,34 @@
         <v>73</v>
       </c>
       <c r="B64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K64" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:11">
@@ -3724,34 +3724,34 @@
         <v>74</v>
       </c>
       <c r="B65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K65" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:11">
@@ -3759,34 +3759,34 @@
         <v>75</v>
       </c>
       <c r="B66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K66" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:11">
@@ -3794,34 +3794,34 @@
         <v>76</v>
       </c>
       <c r="B67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K67" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:11">
@@ -3829,34 +3829,34 @@
         <v>77</v>
       </c>
       <c r="B68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K68" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:11">
@@ -3864,34 +3864,34 @@
         <v>78</v>
       </c>
       <c r="B69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K69" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:11">
@@ -3899,34 +3899,34 @@
         <v>79</v>
       </c>
       <c r="B70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K70" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:11">
@@ -3934,34 +3934,34 @@
         <v>80</v>
       </c>
       <c r="B71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K71" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:11">
@@ -3969,34 +3969,34 @@
         <v>81</v>
       </c>
       <c r="B72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K72" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:11">
@@ -4004,34 +4004,34 @@
         <v>82</v>
       </c>
       <c r="B73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K73" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:11">
@@ -4039,34 +4039,34 @@
         <v>83</v>
       </c>
       <c r="B74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K74" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:11">
@@ -4074,34 +4074,34 @@
         <v>84</v>
       </c>
       <c r="B75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K75" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:11">
@@ -4109,34 +4109,34 @@
         <v>85</v>
       </c>
       <c r="B76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K76" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:11">
@@ -4144,34 +4144,34 @@
         <v>86</v>
       </c>
       <c r="B77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K77" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:11">
@@ -4179,34 +4179,34 @@
         <v>87</v>
       </c>
       <c r="B78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K78" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
